--- a/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$31</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="147">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -283,9 +283,6 @@
     <t>Extension.extension</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
@@ -405,6 +402,27 @@
   </si>
   <si>
     <t>http://example.org/fhir/eu-ai-transparency/ValueSet/ehds-data-category-vs</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose</t>
+  </si>
+  <si>
+    <t>ehdsSecondaryUsePurpose</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:ehdsSecondaryUsePurpose.value[x]</t>
+  </si>
+  <si>
+    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/ehds-secondary-use-purpose-vs</t>
   </si>
   <si>
     <t>Extension.extension:ehdsPermit</t>
@@ -768,12 +786,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.48046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.89453125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.9921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.85546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.26953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -796,7 +814,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1141,7 +1159,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>75</v>
@@ -1156,13 +1174,13 @@
         <v>18</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1201,19 +1219,19 @@
         <v>18</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>74</v>
@@ -1233,13 +1251,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>86</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>18</v>
@@ -1252,7 +1270,7 @@
         <v>79</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -1261,13 +1279,13 @@
         <v>18</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L5" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1318,7 +1336,7 @@
         <v>18</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -1338,10 +1356,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1441,10 +1459,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1467,13 +1485,13 @@
         <v>18</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1512,19 +1530,19 @@
         <v>18</v>
       </c>
       <c r="AB7" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AC7" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AC7" t="s" s="2">
+      <c r="AD7" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE7" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AD7" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE7" t="s" s="2">
+      <c r="AF7" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1544,10 +1562,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1570,16 +1588,16 @@
         <v>18</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1587,7 +1605,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>18</v>
@@ -1629,30 +1647,30 @@
         <v>18</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1675,13 +1693,13 @@
         <v>18</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1732,33 +1750,33 @@
         <v>18</v>
       </c>
       <c r="AF9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI9" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI9" t="s" s="2">
+      <c r="AJ9" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>86</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>18</v>
@@ -1771,7 +1789,7 @@
         <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
@@ -1780,13 +1798,13 @@
         <v>18</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1837,7 +1855,7 @@
         <v>18</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1857,10 +1875,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1960,10 +1978,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1986,13 +2004,13 @@
         <v>18</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2031,19 +2049,19 @@
         <v>18</v>
       </c>
       <c r="AB12" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AC12" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AC12" t="s" s="2">
+      <c r="AD12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE12" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AD12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE12" t="s" s="2">
+      <c r="AF12" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2063,10 +2081,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2089,16 +2107,16 @@
         <v>18</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2106,7 +2124,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>18</v>
@@ -2148,30 +2166,30 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2194,13 +2212,13 @@
         <v>18</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2227,11 +2245,11 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -2249,33 +2267,33 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI14" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AG14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI14" t="s" s="2">
+      <c r="AJ14" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>86</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>18</v>
@@ -2288,7 +2306,7 @@
         <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
@@ -2297,13 +2315,13 @@
         <v>18</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2354,7 +2372,7 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2374,10 +2392,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2477,10 +2495,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2503,13 +2521,13 @@
         <v>18</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2548,19 +2566,19 @@
         <v>18</v>
       </c>
       <c r="AB17" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AC17" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AC17" t="s" s="2">
+      <c r="AD17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AD17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE17" t="s" s="2">
+      <c r="AF17" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2580,10 +2598,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2606,16 +2624,16 @@
         <v>18</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2623,7 +2641,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>18</v>
@@ -2665,30 +2683,30 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2711,13 +2729,13 @@
         <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2744,13 +2762,11 @@
         <v>18</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>18</v>
@@ -2768,46 +2784,46 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI19" t="s" s="2">
+      <c r="AJ19" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AJ19" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AK19" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>86</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -2816,13 +2832,13 @@
         <v>18</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2873,7 +2889,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2893,10 +2909,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2996,10 +3012,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3022,13 +3038,13 @@
         <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>28</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3067,19 +3083,19 @@
         <v>18</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AC22" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AC22" t="s" s="2">
+      <c r="AD22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE22" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AD22" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE22" t="s" s="2">
+      <c r="AF22" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3099,10 +3115,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3125,16 +3141,16 @@
         <v>18</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3142,7 +3158,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>18</v>
@@ -3184,30 +3200,30 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3230,13 +3246,13 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3263,66 +3279,70 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AA24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
-        <v>107</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -3331,24 +3351,22 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>18</v>
@@ -3390,30 +3408,30 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>108</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3424,7 +3442,7 @@
         <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -3436,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3493,26 +3511,543 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="Y29" s="2"/>
+      <c r="Z29" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI26" t="s" s="2">
+      <c r="AJ29" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>108</v>
+      <c r="AK29" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK26">
+  <autoFilter ref="A1:AK31">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -3522,7 +4057,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI25">
+  <conditionalFormatting sqref="A2:AI30">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Details regarding provenance, EHDS categories, and data quality.</t>
+    <t>Documents the origin, relevant EHDS-related classifications, applicable permit identifiers, secondary-use purposes, and reported quality characteristics of data used to train or develop the AI system.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>79</v>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>79</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ai-training-data.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/StructureDefinition/ai-training-data</t>
+    <t>http://example.org/fhir/trust-ai-transparency/StructureDefinition/ai-training-data</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:39:53+00:00</t>
+    <t>2026-09-09T11:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -376,22 +376,22 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:ehdsCategory</t>
-  </si>
-  <si>
-    <t>ehdsCategory</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsCategory.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsCategory.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsCategory.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsCategory.value[x]</t>
+    <t>Extension.extension:Category</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Extension.extension:Category.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:Category.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:Category.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:Category.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -401,46 +401,46 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/ehds-data-category-vs</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsSecondaryUsePurpose</t>
-  </si>
-  <si>
-    <t>ehdsSecondaryUsePurpose</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsSecondaryUsePurpose.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsSecondaryUsePurpose.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsSecondaryUsePurpose.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsSecondaryUsePurpose.value[x]</t>
-  </si>
-  <si>
-    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/ehds-secondary-use-purpose-vs</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsPermit</t>
-  </si>
-  <si>
-    <t>ehdsPermit</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsPermit.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsPermit.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsPermit.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:ehdsPermit.value[x]</t>
+    <t>http://example.org/fhir/trust-ai-transparency/ValueSet/data-category-vs</t>
+  </si>
+  <si>
+    <t>Extension.extension:SecondaryUsePurpose</t>
+  </si>
+  <si>
+    <t>SecondaryUsePurpose</t>
+  </si>
+  <si>
+    <t>Extension.extension:SecondaryUsePurpose.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:SecondaryUsePurpose.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:SecondaryUsePurpose.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:SecondaryUsePurpose.value[x]</t>
+  </si>
+  <si>
+    <t>http://example.org/fhir/trust-ai-transparency/ValueSet/secondary-use-purpose-vs</t>
+  </si>
+  <si>
+    <t>Extension.extension:Permit</t>
+  </si>
+  <si>
+    <t>Permit</t>
+  </si>
+  <si>
+    <t>Extension.extension:Permit.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:Permit.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:Permit.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:Permit.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -465,7 +465,7 @@
     <t>Extension.extension:dataQuality.value[x]</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/eu-ai-data-quality-vs</t>
+    <t>http://example.org/fhir/trust-ai-transparency/ValueSet/trust-ai-data-quality-vs</t>
   </si>
   <si>
     <t>base64Binary
@@ -789,9 +789,9 @@
   <dimension ref="A1:AK31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.89453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.1171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.9921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.26953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.4921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -814,7 +814,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.7734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
